--- a/brunei/budget_layer_all_years.xlsx
+++ b/brunei/budget_layer_all_years.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">

--- a/brunei/budget_layer_all_years.xlsx
+++ b/brunei/budget_layer_all_years.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,21 @@
           <t>source_file</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>programme_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>class_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>strategy_name_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,6 +525,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,6 +577,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,6 +637,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,6 +697,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,6 +757,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -760,6 +817,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,6 +877,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -860,6 +937,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -910,6 +997,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -960,6 +1057,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1010,6 +1117,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1060,6 +1177,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1110,6 +1237,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1160,6 +1297,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1210,6 +1357,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1260,6 +1417,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1310,6 +1477,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1360,6 +1537,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1410,6 +1597,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1460,6 +1657,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1510,6 +1717,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1560,6 +1777,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1610,6 +1837,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1650,6 +1887,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1700,6 +1939,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1750,6 +1999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1800,6 +2059,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1850,6 +2119,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1900,6 +2179,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1950,6 +2239,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2000,6 +2299,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2050,6 +2359,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2100,6 +2419,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2150,6 +2479,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2200,6 +2539,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2250,6 +2599,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2290,6 +2649,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2340,6 +2701,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2390,6 +2761,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2440,6 +2821,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2490,6 +2881,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2540,6 +2941,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2590,6 +3001,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2638,6 +3059,16 @@
       <c r="J45" t="inlineStr">
         <is>
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brunei/brunei_budget_2025.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>

--- a/brunei/budget_layer_all_years.xlsx
+++ b/brunei/budget_layer_all_years.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="budget_all_years" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs_wide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="national_total" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3939,7 +3940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3950,27 +3951,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>head_total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>strategy_total</t>
+          <t>programme_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>program_sum</t>
+          <t>gap_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nested_heads</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -3980,76 +3986,25 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>3068.44</v>
       </c>
       <c r="C2" t="n">
-        <v>1949.77</v>
+        <v>3032.97</v>
       </c>
       <c r="D2" t="n">
-        <v>1912.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.27000000000021</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>493.77</v>
-      </c>
-      <c r="D3" t="n">
-        <v>493.77</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-5.684341886080801e-14</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>626.6999999999999</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.799999999999955</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
+        <v>1.16</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3068.44</v>
       </c>
     </row>
   </sheetData>
@@ -4069,6 +4024,130 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>strategy_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>strategy_total</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>program_sum</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1949.77</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1912.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.27000000000021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>493.77</v>
+      </c>
+      <c r="D3" t="n">
+        <v>493.77</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-5.684341886080801e-14</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>626.6999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.799999999999955</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>severity</t>
         </is>
       </c>

--- a/brunei/budget_layer_all_years.xlsx
+++ b/brunei/budget_layer_all_years.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,11 @@
           <t>strategy_name_source</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>countable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,6 +533,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,6 +594,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,6 +659,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,6 +724,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,6 +789,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,6 +854,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -888,6 +919,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -948,6 +984,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1008,6 +1049,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1068,6 +1114,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1128,6 +1179,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1188,6 +1244,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1248,6 +1309,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1308,6 +1374,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1368,6 +1439,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1428,6 +1504,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1488,6 +1569,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1548,6 +1634,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1608,6 +1699,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1668,6 +1764,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1728,6 +1829,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1788,6 +1894,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1848,6 +1959,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1890,6 +2006,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1950,6 +2067,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2010,6 +2132,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2070,6 +2197,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2130,6 +2262,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2190,6 +2327,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2250,6 +2392,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2310,6 +2457,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2370,6 +2522,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2430,6 +2587,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2490,6 +2652,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2550,6 +2717,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2610,6 +2782,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2652,6 +2829,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2712,6 +2890,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2772,6 +2955,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2832,6 +3020,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2892,6 +3085,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2952,6 +3150,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3012,6 +3215,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3070,6 +3278,11 @@
       <c r="L45" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/brunei/budget_layer_all_years.xlsx
+++ b/brunei/budget_layer_all_years.xlsx
@@ -4153,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4174,20 +4174,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>grand_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>extracted_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>gap_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>nested_heads</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>national</t>
         </is>
@@ -4205,18 +4215,20 @@
       <c r="C2" t="n">
         <v>3032.97</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
         <v>1.16</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>heads</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>3068.44</v>
       </c>
     </row>
@@ -4284,7 +4296,7 @@
         <v>1912.5</v>
       </c>
       <c r="E2" t="n">
-        <v>37.27000000000021</v>
+        <v>37.26999999999975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4355,7 +4367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4449,12 +4461,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>no_grand_total</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4465,6 +4477,30 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>the document printed no grand total that stage 5 could find, so there is nothing to check the extraction's completeness against. Every share for FY2025 rests on the heads being all of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>national budget total = 3,068.4</t>
         </is>
